--- a/vse-loti/340609789/spec-340609789.xlsx
+++ b/vse-loti/340609789/spec-340609789.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>тонна</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="G4" s="8" t="n">
-        <v>1013114.754098361</v>
+        <v>1013114.75</v>
       </c>
     </row>
     <row r="5">
@@ -592,19 +592,18 @@
         <v>1236000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Источник: Документация на проведение ЭА СМСП (трубы).docx (Раздел 4 п. 3 — кол-во; Раздел 7 — обоснование Н(М)ЦД)
-Извещение о закупке № 32616373252 (данные из ВСРЗ).htm</t>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Источник: Документация на проведение ЭА СМСП (трубы).docx</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="A7:B9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
